--- a/models/xls/BeModelPatientWill.xlsx
+++ b/models/xls/BeModelPatientWill.xlsx
@@ -500,7 +500,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
@@ -931,23 +930,11 @@
           <t>Data Element</t>
         </is>
       </c>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="n"/>
-      <c r="I1" s="1" t="n"/>
-      <c r="J1" s="1" t="n"/>
-      <c r="K1" s="1" t="n"/>
-      <c r="L1" s="1" t="n"/>
-      <c r="M1" s="1" t="n"/>
       <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Common Glossary</t>
         </is>
       </c>
-      <c r="O1" s="1" t="n"/>
       <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Example Value</t>
@@ -1068,6 +1055,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>RecordedDate</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>equivalent</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1103,6 +1100,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>BusinessIdentifier</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>equivalent</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1138,6 +1145,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Patient</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>equivalent</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1173,6 +1190,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Recorder</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>equivalent</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1348,6 +1375,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>equivalent</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1556,6 +1593,16 @@
       <c r="K17" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>equivalent</t>
         </is>
       </c>
     </row>
